--- a/out/Attention-mamba2_repeat_3_000006.xlsx
+++ b/out/Attention-mamba2_repeat_3_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.6780933625747478</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.6780933625747478</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003128222096160753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4026263409910837</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.806015066578293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09298306858678258</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3093304501946852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3093304501946852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3089949417553572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.030754323529692</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.372556386773466</v>
+        <v>-1.47215856204275e-05</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1972232256246942</v>
+        <v>-0.01373640914256689</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.734744129634345</v>
+        <v>-0.01375113072818727</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3454551839555684</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.228528260576171</v>
+        <v>-0.01376722205868724</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1891838300539991</v>
+        <v>0.0002759585735690626</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.26114301674595</v>
+        <v>-0.01130992583272629</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07813567695078479</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.22803213394136</v>
+        <v>-0.01567811964707996</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.09735034832865293</v>
+        <v>0.01583773363034061</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.34461085647105</v>
+        <v>0.01822634797461529</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05861748466870621</v>
+        <v>0.01081071749787676</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.36442961625947</v>
+        <v>0.02399028752456966</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0445650463841772</v>
+        <v>0.009840873775819119</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.394917792165746</v>
+        <v>0.03285627512308804</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01971203038416808</v>
+        <v>0.004169942565760353</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.389735703386273</v>
+        <v>0.03134593439155608</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01564027987761302</v>
+        <v>0.003765458507715891</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.854026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.401299760912972</v>
+        <v>0.03470619130317121</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.007754591776772256</v>
+        <v>0.001861529395804215</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.6780933625747478</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.401156271458186</v>
+        <v>0.03466090056340687</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004507170356471418</v>
+        <v>0.001112146635430454</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.6780933625747478</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.402411921959817</v>
+        <v>0.03502288090542168</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002249630577862894</v>
+        <v>0.000554811839483997</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.402404114792548</v>
+        <v>0.03501706229922455</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001110363487004101</v>
+        <v>0.0002710014778349926</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.402370880486227</v>
+        <v>0.03500383942135249</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006425046389131309</v>
+        <v>0.0001577077519095283</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.402544939550174</v>
+        <v>0.03505099013472081</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.000211501101055275</v>
+        <v>4.539476136470093e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.254026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.40232490697687</v>
+        <v>0.03498281186537026</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001027979750690101</v>
+        <v>2.039087514853836e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9612393007297437</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.402321113622841</v>
+        <v>0.03497817360543902</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.370870712260415e-05</v>
+        <v>9.098272454131421e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.854026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.402325871683893</v>
+        <v>0.0349761618306574</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.344216536355913e-05</v>
+        <v>2.752092955494119e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.854026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.402318933314006</v>
+        <v>0.03497054107636562</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>-4.591292492038157e-08</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9612393007297437</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.4023209272638</v>
+        <v>0.03496769250366348</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.854661261639439e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9612393007297437</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.402313592869656</v>
+        <v>0.03496202507338987</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.561239300729744</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.402310107649348</v>
+        <v>0.03496240560844762</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.561239300729744</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.402305560337163</v>
+        <v>0.03496263392948231</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.561239300729744</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.402305650281813</v>
+        <v>0.03496272387413238</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.402304792348227</v>
+        <v>0.03496186594054755</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.402305020669262</v>
+        <v>0.03496209426158212</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.402304225005051</v>
+        <v>0.03496129859737039</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.402304287274423</v>
+        <v>0.03496136086674349</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.402304314949701</v>
+        <v>0.03496138854202046</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.402304467163723</v>
+        <v>0.03496154075604351</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.402304121222762</v>
+        <v>0.03496119481508189</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9612393007297437</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.402304197329773</v>
+        <v>0.03496127092209354</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.854026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.402304363381435</v>
+        <v>0.03496143697375513</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.402304723160035</v>
+        <v>0.03496179675235517</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9612393007297437</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.402304743916493</v>
+        <v>0.03496181750881288</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.561239300729744</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.402304847698781</v>
+        <v>0.03496192129110137</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.561239300729744</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.402305076019816</v>
+        <v>0.03496214961213607</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.561239300729744</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.40230495148107</v>
+        <v>0.03496202507338987</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.254026995542006</v>
+        <v>2.303898596494605</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.402304979156347</v>
+        <v>0.03496205274866673</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.402305034506901</v>
+        <v>0.03496210809922067</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9612393007297437</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.402305297422032</v>
+        <v>0.03496237101435149</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.4023052143962</v>
+        <v>0.03496228798852069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.402305006831623</v>
+        <v>0.0349620804239437</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.402305020669262</v>
+        <v>0.03496209426158212</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.402305159045647</v>
+        <v>0.03496223263796687</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.402304875374058</v>
+        <v>0.03496194896637835</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.402304702403578</v>
+        <v>0.03496177599589748</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.402304598621289</v>
+        <v>0.03496167221360898</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.402304743916493</v>
+        <v>0.03496181750881288</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.402304986075166</v>
+        <v>0.034962059667486</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.402304813104685</v>
+        <v>0.03496188669700525</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.402304515595458</v>
+        <v>0.03496158918777818</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.40230450175782</v>
+        <v>0.03496157535013976</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.4023041350604</v>
+        <v>0.03496120865272044</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.854026995542006</v>
+        <v>1.703898596494605</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.4023041350604</v>
+        <v>0.03496120865272044</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.402304072791027</v>
+        <v>0.03496114638334734</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.402303969008738</v>
+        <v>0.03496104260105884</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.402303796038258</v>
+        <v>0.03496086963057798</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.402303844469992</v>
+        <v>0.03496091806231264</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.402303484691393</v>
+        <v>0.03496055828371248</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.402303443178477</v>
+        <v>0.03496051677079708</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.402303498529031</v>
+        <v>0.03496057212135103</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.402303553879585</v>
+        <v>0.03496062747190485</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.4023035953925</v>
+        <v>0.03496066898482025</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.40230332555855</v>
+        <v>0.03496039915087016</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.402303380909104</v>
+        <v>0.03496045450142399</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.402303526204308</v>
+        <v>0.03496059979662788</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.402303491610212</v>
+        <v>0.03496056520253175</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.402303477772573</v>
+        <v>0.03496055136489332</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.402303567717223</v>
+        <v>0.03496064130954328</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.402303885982908</v>
+        <v>0.03496095957522805</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.402303706093608</v>
+        <v>0.03496077968592802</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.402303747606523</v>
+        <v>0.03496082119884342</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.402303560798404</v>
+        <v>0.03496063439072412</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.402303629986596</v>
+        <v>0.03496070357891638</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.402303429340839</v>
+        <v>0.03496050293315866</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.402303470853755</v>
+        <v>0.03496054444607406</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>-4.305869758048653e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.278093362574748</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.402303498529031</v>
+        <v>0.03496057212135103</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000006.xlsx
+++ b/out/Attention-mamba2_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.6636503946122936</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003128222096160753</v>
+        <v>-0.0002468063315673498</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4026263409910837</v>
+        <v>0.3176589740151539</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.806015066578293</v>
+        <v>0.6359191116119842</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09298306858678258</v>
+        <v>-0.07336051391005742</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3093304501946852</v>
+        <v>0.244051653773529</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3093304501946852</v>
+        <v>0.244051653773529</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3089949417553572</v>
+        <v>0.2437931666727169</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.030754323529692</v>
+        <v>0.7941282765247593</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.372556386773466</v>
+        <v>1.833631014730753</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1972232256246942</v>
+        <v>0.1519474977506417</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.734744129634345</v>
+        <v>1.342238858901299</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3454551839555684</v>
+        <v>0.2661504527206348</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.228528260576171</v>
+        <v>1.722666750086819</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1891838300539991</v>
+        <v>0.1457534350213512</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.26114301674595</v>
+        <v>1.747794238761166</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07813567695078479</v>
+        <v>0.06019829131297767</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.22803213394136</v>
+        <v>1.722284508305738</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.09735034832865293</v>
+        <v>0.07500190510666892</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.34461085647105</v>
+        <v>1.8121007193194</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05861748466870621</v>
+        <v>0.04516142564025537</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.36442961625947</v>
+        <v>1.82736978775652</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0445650463841772</v>
+        <v>0.03433482415372246</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.394917792165746</v>
+        <v>1.850858712394061</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01971203038416808</v>
+        <v>0.01518545356264268</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.389735703386273</v>
+        <v>1.846866236866692</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01564027987761302</v>
+        <v>0.01204865025553967</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.401299760912972</v>
+        <v>1.855774642637109</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.007754591776772256</v>
+        <v>0.005973537829299062</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.401156271458186</v>
+        <v>1.855662940574911</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004507170356471418</v>
+        <v>0.003471494891027301</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.402411921959817</v>
+        <v>1.856629234804085</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002249630577862894</v>
+        <v>0.001731792845140836</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.402404114792548</v>
+        <v>1.856622072379751</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001110363487004101</v>
+        <v>0.000854519800552129</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.402370880486227</v>
+        <v>1.856595314499364</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006425046389131309</v>
+        <v>0.0004923102639075078</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.402544939550174</v>
+        <v>1.856728302805243</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.000211501101055275</v>
+        <v>0.0001623977585478931</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.40232490697687</v>
+        <v>1.856557040506296</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001027979750690101</v>
+        <v>7.809427244902859e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.402321113622841</v>
+        <v>1.856552973800357</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.370870712260415e-05</v>
+        <v>4.147772647206162e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.402325871683893</v>
+        <v>1.856555540087465</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.344216536355913e-05</v>
+        <v>1.633162402266935e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.402318933314006</v>
+        <v>1.856549067283297</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.4023209272638</v>
+        <v>1.856549445851543</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.402313592869656</v>
+        <v>1.856542778887672</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.402310107649348</v>
+        <v>1.856538916812576</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.402305560337163</v>
+        <v>1.856534369500391</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.402305650281813</v>
+        <v>1.856534459445041</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.402304792348227</v>
+        <v>1.856533601511456</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.402305020669262</v>
+        <v>1.85653382983249</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.402304225005051</v>
+        <v>1.856533034168279</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.402304287274423</v>
+        <v>1.856533096437652</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.402304314949701</v>
+        <v>1.856533124112929</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.402304467163723</v>
+        <v>1.856533276326952</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.402304121222762</v>
+        <v>1.85653293038599</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.402304197329773</v>
+        <v>1.856533006493002</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.402304363381435</v>
+        <v>1.856533172544663</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.402304723160035</v>
+        <v>1.856533532323263</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.402304743916493</v>
+        <v>1.856533553079721</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.402304847698781</v>
+        <v>1.856533656862009</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.402305076019816</v>
+        <v>1.856533885183044</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.40230495148107</v>
+        <v>1.856533760644298</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.402304979156347</v>
+        <v>1.856533788319575</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.402305034506901</v>
+        <v>1.856533843670129</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.402305297422032</v>
+        <v>1.85653410658526</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.4023052143962</v>
+        <v>1.856534023559429</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.402305006831623</v>
+        <v>1.856533815994852</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.402305020669262</v>
+        <v>1.85653382983249</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.402305159045647</v>
+        <v>1.856533968208875</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.402304875374058</v>
+        <v>1.856533684537286</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.402304702403578</v>
+        <v>1.856533511566806</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.402304598621289</v>
+        <v>1.856533407784517</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.402304743916493</v>
+        <v>1.856533553079721</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.402304986075166</v>
+        <v>1.856533795238394</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.402304813104685</v>
+        <v>1.856533622267914</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.402304515595458</v>
+        <v>1.856533324758687</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.40230450175782</v>
+        <v>1.856533310921048</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.4023041350604</v>
+        <v>1.856532944223628</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.854026995542006</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.4023041350604</v>
+        <v>1.856532944223628</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.402304072791027</v>
+        <v>1.856532881954255</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.254026995542006</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.402303969008738</v>
+        <v>1.856532778171967</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.254026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.402303796038258</v>
+        <v>1.856532605201486</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.402303844469992</v>
+        <v>1.856532653633221</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.402303484691393</v>
+        <v>1.856532293854621</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.402303443178477</v>
+        <v>1.856532252341705</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.402303498529031</v>
+        <v>1.856532307692259</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.402303553879585</v>
+        <v>1.856532363042813</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.4023035953925</v>
+        <v>1.856532404555729</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.40230332555855</v>
+        <v>1.856532134721778</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.254026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.402303380909104</v>
+        <v>1.856532190072332</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.254026995542006</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.402303526204308</v>
+        <v>1.856532335367536</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.254026995542006</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.402303491610212</v>
+        <v>1.85653230077344</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.254026995542006</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.402303477772573</v>
+        <v>1.856532286935802</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.254026995542006</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.402303567717223</v>
+        <v>1.856532376880452</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.402303885982908</v>
+        <v>1.856532695146136</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.254026995542006</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.402303706093608</v>
+        <v>1.856532515256836</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.254026995542006</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.402303747606523</v>
+        <v>1.856532556769751</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.854026995542006</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.402303560798404</v>
+        <v>1.856532369961633</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.402303629986596</v>
+        <v>1.856532439149824</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.402303429340839</v>
+        <v>1.856532238504067</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.402303470853755</v>
+        <v>1.856532280016983</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.854026995542006</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.402303498529031</v>
+        <v>1.856532307692259</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000006.xlsx
+++ b/out/Attention-mamba2_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1913402229547501</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1944755613803864</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.2024868875741959</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.2268766313791275</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1906379908323288</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.2081245332956314</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1978408843278885</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.2629232704639435</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2682049572467804</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.2302500456571579</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1969083696603775</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.1987148970365524</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.2326014786958694</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2049890607595444</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.1980857998132706</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.1977785676717758</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.2170859128236771</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.2443125993013382</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.3009730279445648</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.2450711280107498</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.2318438440561295</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.2037455588579178</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.2106239944696426</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.2669335007667542</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.218867227435112</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2758914828300476</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.08966991305351257</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.09720325469970703</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.3114745914936066</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.3077307939529419</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.2330109626054764</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2040921300649643</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.2240670770406723</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.1084407716989517</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.3338589370250702</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.01612649947684253</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.3243370652198792</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.3737601041793823</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2862685918807983</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.3204299807548523</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.1282668709754944</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.06112434715032578</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.04379944875836372</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02106145024299622</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002468063315673498</v>
+        <v>-0.0001987187176558655</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3176589740151539</v>
+        <v>0.2557662586041952</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.008617516607046127</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6359191116119842</v>
+        <v>0.5120169718848381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07336051391005742</v>
+        <v>-0.05906703913986523</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.006101995706558228</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.244051653773529</v>
+        <v>0.1965005007466741</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.003957446664571762</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.244051653773529</v>
+        <v>0.1965005007466741</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01290276646614075</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2437931666727169</v>
+        <v>0.1963969839172822</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7941282765247593</v>
+        <v>0.3180260874068487</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02415384352207184</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6313973956586085</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.833631014730753</v>
+        <v>0.8330824230025851</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1519474977506417</v>
+        <v>0.06085070841749696</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.008724462240934372</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.342238858901299</v>
+        <v>0.6362936555949487</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2661504527206348</v>
+        <v>0.1065855692215107</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.008377138525247574</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.722666750086819</v>
+        <v>0.7886443496492561</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1457534350213512</v>
+        <v>0.05837037468004286</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01772673055529594</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.747794238761166</v>
+        <v>0.7987072240189123</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06019829131297767</v>
+        <v>0.02410781480739816</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0183117538690567</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.722284508305738</v>
+        <v>0.7884912886057727</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07500190510666892</v>
+        <v>0.0300362684567398</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.04125170782208443</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4313973956586085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.8121007193194</v>
+        <v>0.8244600571006301</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04516142564025537</v>
+        <v>0.01808512287435136</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.04661713168025017</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.82736978775652</v>
+        <v>0.8305748339571098</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03433482415372246</v>
+        <v>0.01374982751801625</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.07706409692764282</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4313973956586085</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.850858712394061</v>
+        <v>0.8399810821114243</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01518545356264268</v>
+        <v>0.006078810026971771</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.05057373270392418</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4313973956586085</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.846866236866692</v>
+        <v>0.8383791725318499</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01204865025553967</v>
+        <v>0.004822513410567679</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.027295196428895</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.855774642637109</v>
+        <v>0.8419436370413454</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005973537829299062</v>
+        <v>0.00238891661198293</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01991196349263191</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.855662940574911</v>
+        <v>0.8418959115712517</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003471494891027301</v>
+        <v>0.00138559795641092</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01103080436587334</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.856629234804085</v>
+        <v>0.8422798374732563</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001731792845140836</v>
+        <v>0.0006902989782054602</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01943745836615562</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.856622072379751</v>
+        <v>0.842273971779092</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000854519800552129</v>
+        <v>0.0003399577794858043</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.02248933538794518</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.856595314499364</v>
+        <v>0.8422602395194048</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004923102639075078</v>
+        <v>0.0001952591666741642</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.03760605677962303</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4313973956586085</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.856728302805243</v>
+        <v>0.8423106186113472</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001623977585478931</v>
+        <v>6.195910341915722e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01073559373617172</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.856557040506296</v>
+        <v>0.8422391136917688</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.809427244902859e-05</v>
+        <v>2.868686720906565e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.006743837147951126</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.856552973800357</v>
+        <v>0.8422344864443727</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>1.212337291075954e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001639701426029205</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.856555540087465</v>
+        <v>0.8422324746695913</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.0004704669117927551</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.01612649947684253</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.856549067283297</v>
+        <v>0.8422268539152995</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01576640829443932</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.856549445851543</v>
+        <v>0.8422240053425976</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0002725832164287567</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.856542778887672</v>
+        <v>0.8422183379123239</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01545415446162224</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.856538916812576</v>
+        <v>0.8422187184473816</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.001940559595823288</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.856534369500391</v>
+        <v>0.8422189467684164</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01251709833741188</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.856534459445041</v>
+        <v>0.8422190367130663</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.000294901430606842</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.856533601511456</v>
+        <v>0.8422181787794815</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.009658258408308029</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.85653382983249</v>
+        <v>0.8422184071005161</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01364056393504143</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.01612649947684253</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.856533034168279</v>
+        <v>0.8422176114363044</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.006922259926795959</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.6313973956586085</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.856533096437652</v>
+        <v>0.8422176737056775</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.002058722078800201</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.856533124112929</v>
+        <v>0.8422177013809543</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.009432408958673477</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.856533276326952</v>
+        <v>0.8422178535949777</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.003491919487714767</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.85653293038599</v>
+        <v>0.8422175076540159</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001162983477115631</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.856533006493002</v>
+        <v>0.8422175837610275</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.02035980671644211</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.856533172544663</v>
+        <v>0.8422177498126892</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.0006294287741184235</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.856533532323263</v>
+        <v>0.8422181095912892</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.008259594440460205</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.856533553079721</v>
+        <v>0.8422181303477468</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0142652653157711</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.856533656862009</v>
+        <v>0.8422182341300354</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001939624547958374</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.856533885183044</v>
+        <v>0.8422184624510701</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.004651501774787903</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.856533760644298</v>
+        <v>0.8422183379123239</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.02596906200051308</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.856533788319575</v>
+        <v>0.8422183655876008</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.006125964224338531</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.856533843670129</v>
+        <v>0.8422184209381547</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.004082027822732925</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.85653410658526</v>
+        <v>0.8422186838532854</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.005552452057600021</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.856534023559429</v>
+        <v>0.8422186008274546</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.02573654428124428</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.856533815994852</v>
+        <v>0.8422183932628778</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.02794375643134117</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.85653382983249</v>
+        <v>0.8422184071005161</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.02676088735461235</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.856533968208875</v>
+        <v>0.8422185454769009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.02912146598100662</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.856533684537286</v>
+        <v>0.8422182618053122</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.02835822850465775</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.856533511566806</v>
+        <v>0.8422180888348315</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.001730576157569885</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.856533407784517</v>
+        <v>0.842217985052543</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.02944717928767204</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.856533553079721</v>
+        <v>0.8422181303477468</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02915409579873085</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.856533795238394</v>
+        <v>0.8422183725064202</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.02960276231169701</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.856533622267914</v>
+        <v>0.8422181995359391</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0296849999576807</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.856533324758687</v>
+        <v>0.8422179020267122</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02937005832791328</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.856533310921048</v>
+        <v>0.8422178881890736</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.03123931586742401</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.856532944223628</v>
+        <v>0.8422175214916544</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02489614114165306</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6313973956586085</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.856532944223628</v>
+        <v>0.8422175214916544</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.008393201977014542</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6313973956586085</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.856532881954255</v>
+        <v>0.8422174592222813</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0308460034430027</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.856532778171967</v>
+        <v>0.8422173554399929</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.03068006783723831</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.856532605201486</v>
+        <v>0.842217182469512</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.005868095904588699</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.278921290794059</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.856532653633221</v>
+        <v>0.8422172309012467</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.03441732004284859</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.856532293854621</v>
+        <v>0.8422168711226466</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.03066841699182987</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.856532252341705</v>
+        <v>0.8422168296097312</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.02844017744064331</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.856532307692259</v>
+        <v>0.8422168849602849</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03194884955883026</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.856532363042813</v>
+        <v>0.8422169403108388</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.04098686203360558</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.856532404555729</v>
+        <v>0.8422169818237543</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.03673569113016129</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.856532134721778</v>
+        <v>0.8422167119898042</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.04104301333427429</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.856532190072332</v>
+        <v>0.8422167673403581</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.04046512395143509</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.078921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.856532335367536</v>
+        <v>0.842216912635562</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.04020074382424355</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.078921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.85653230077344</v>
+        <v>0.8422168780414657</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.03057575412094593</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.856532286935802</v>
+        <v>0.8422168642038272</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02906996011734009</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.856532376880452</v>
+        <v>0.8422169541484774</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01411747559905052</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.856532695146136</v>
+        <v>0.8422172724141621</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.008495412766933441</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.856532515256836</v>
+        <v>0.8422170925248619</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.004064943641424179</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.856532556769751</v>
+        <v>0.8422171340377773</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.003830190747976303</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.856532369961633</v>
+        <v>0.842216947229658</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.03032876923680305</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.856532439149824</v>
+        <v>0.8422170164178505</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.02901438251137733</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.856532238504067</v>
+        <v>0.8422168157720926</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.03119392320513725</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7900000000000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.856532280016983</v>
+        <v>0.8422168572850081</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.06000718474388123</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.278921290794059</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.856532307692259</v>
+        <v>0.8422168849602849</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000006.xlsx
+++ b/out/Attention-mamba2_repeat_3_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1913402229547501</v>
+        <v>-0.1904544234275818</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1944755613803864</v>
+        <v>-0.1937772184610367</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.2024868875741959</v>
+        <v>-0.2019574493169785</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.2268766313791275</v>
+        <v>-0.2263306826353073</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1906379908323288</v>
+        <v>-0.1902273148298264</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.2081245332956314</v>
+        <v>-0.2077763229608536</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1978408843278885</v>
+        <v>-0.1971154361963272</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.2629232704639435</v>
+        <v>-0.2621398270130157</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2682049572467804</v>
+        <v>-0.26743084192276</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.2302500456571579</v>
+        <v>-0.2297142595052719</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1969083696603775</v>
+        <v>-0.1965005993843079</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.1987148970365524</v>
+        <v>-0.1983423084020615</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.2326014786958694</v>
+        <v>-0.2323761433362961</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2049890607595444</v>
+        <v>-0.2046516388654709</v>
       </c>
       <c r="JB15" t="n">
         <v>0.02000000000000007</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.1980857998132706</v>
+        <v>-0.1977725476026535</v>
       </c>
       <c r="JB16" t="n">
         <v>0.1600000000000001</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.1977785676717758</v>
+        <v>-0.1974483877420425</v>
       </c>
       <c r="JB17" t="n">
         <v>0.16</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.2170859128236771</v>
+        <v>-0.2167581170797348</v>
       </c>
       <c r="JB18" t="n">
         <v>0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.2443125993013382</v>
+        <v>-0.2438103407621384</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.3009730279445648</v>
+        <v>-0.3006468117237091</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.2599999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.2450711280107498</v>
+        <v>-0.2446742206811905</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.2318438440561295</v>
+        <v>-0.2315611988306046</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.2037455588579178</v>
+        <v>-0.2034036666154861</v>
       </c>
       <c r="JB23" t="n">
         <v>0.1600000000000001</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.2106239944696426</v>
+        <v>-0.2102331668138504</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.2669335007667542</v>
+        <v>-0.2667352557182312</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.218867227435112</v>
+        <v>-0.2183134704828262</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2758914828300476</v>
+        <v>-0.2755017876625061</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.08966991305351257</v>
+        <v>0.08857122808694839</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.09720325469970703</v>
+        <v>0.09630128741264343</v>
       </c>
       <c r="JB29" t="n">
         <v>0.1600000000000001</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.3114745914936066</v>
+        <v>-0.3104827702045441</v>
       </c>
       <c r="JB30" t="n">
         <v>0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.3077307939529419</v>
+        <v>-0.3073567450046539</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.2330109626054764</v>
+        <v>-0.2326599210500717</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.8599999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2040921300649643</v>
+        <v>-0.2037442773580551</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.2240670770406723</v>
+        <v>-0.2234043329954147</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.1084407716989517</v>
+        <v>0.107685774564743</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.3338589370250702</v>
+        <v>-0.3329257369041443</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.3243370652198792</v>
+        <v>-0.3234538435935974</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.3737601041793823</v>
+        <v>-0.3733135759830475</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2862685918807983</v>
+        <v>-0.2856100499629974</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.3204299807548523</v>
+        <v>-0.3195689618587494</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.1282668709754944</v>
+        <v>0.1277645826339722</v>
       </c>
       <c r="JB41" t="n">
         <v>0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.06112434715032578</v>
+        <v>0.06014159321784973</v>
       </c>
       <c r="JB42" t="n">
         <v>0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.04379944875836372</v>
+        <v>0.04273181781172752</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.02106145024299622</v>
+        <v>0.02001568302512169</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.008617516607046127</v>
+        <v>0.007580384612083435</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.006101995706558228</v>
+        <v>0.005031842738389969</v>
       </c>
       <c r="JB46" t="n">
         <v>0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.003957446664571762</v>
+        <v>0.002868663519620895</v>
       </c>
       <c r="JB47" t="n">
         <v>0.5799999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01290276646614075</v>
+        <v>0.01190690696239471</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.16</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.02415384352207184</v>
+        <v>0.0232558436691761</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.02000000000000007</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.008724462240934372</v>
+        <v>-0.009690146893262863</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.008377138525247574</v>
+        <v>0.007486015558242798</v>
       </c>
       <c r="JB51" t="n">
         <v>0.1199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.01772673055529594</v>
+        <v>-0.01859570667147636</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.02000000000000007</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.0183117538690567</v>
+        <v>0.01740605756640434</v>
       </c>
       <c r="JB53" t="n">
         <v>0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.04125170782208443</v>
+        <v>-0.04204459860920906</v>
       </c>
       <c r="JB54" t="n">
         <v>0.5799999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.04661713168025017</v>
+        <v>0.04611055180430412</v>
       </c>
       <c r="JB55" t="n">
         <v>0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.07706409692764282</v>
+        <v>-0.07773788273334503</v>
       </c>
       <c r="JB56" t="n">
         <v>0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.05057373270392418</v>
+        <v>0.03903673216700554</v>
       </c>
       <c r="JB57" t="n">
         <v>0.8599999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.027295196428895</v>
+        <v>0.02683581970632076</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.01991196349263191</v>
+        <v>-0.02073702588677406</v>
       </c>
       <c r="JB59" t="n">
         <v>0.8599999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.01103080436587334</v>
+        <v>-0.01181304827332497</v>
       </c>
       <c r="JB60" t="n">
         <v>0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.01943745836615562</v>
+        <v>-0.02043548598885536</v>
       </c>
       <c r="JB61" t="n">
         <v>0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.02248933538794518</v>
+        <v>0.008530035614967346</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.03760605677962303</v>
+        <v>-0.0385698564350605</v>
       </c>
       <c r="JB63" t="n">
         <v>0.1199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.01073559373617172</v>
+        <v>0.009937211871147156</v>
       </c>
       <c r="JB64" t="n">
         <v>0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.006743837147951126</v>
+        <v>-0.007461715489625931</v>
       </c>
       <c r="JB65" t="n">
         <v>0.1199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.001639701426029205</v>
+        <v>0.0009391307830810547</v>
       </c>
       <c r="JB66" t="n">
         <v>0.1199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.0004704669117927551</v>
+        <v>-0.0003050491213798523</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.02000000000000007</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.01576640829443932</v>
+        <v>-0.008993253111839294</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0002725832164287567</v>
+        <v>-0.001046415418386459</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.01545415446162224</v>
+        <v>-0.01618025824427605</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.5799999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.001940559595823288</v>
+        <v>-0.002474214881658554</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.5799999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.01251709833741188</v>
+        <v>-0.01325555518269539</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.000294901430606842</v>
+        <v>-0.0008171945810317993</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.009658258408308029</v>
+        <v>-0.01038474217057228</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.5799999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.01364056393504143</v>
+        <v>-0.01190720126032829</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.4399999999999999</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.006922259926795959</v>
+        <v>0.006541047245264053</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0.8422176737056775</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.002058722078800201</v>
+        <v>0.001590229570865631</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0.8422177013809543</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.009432408958673477</v>
+        <v>-0.0102044977247715</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0.8422178535949777</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.003491919487714767</v>
+        <v>0.003136925399303436</v>
       </c>
       <c r="JB79" t="n">
         <v>0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001162983477115631</v>
+        <v>-0.001525398343801498</v>
       </c>
       <c r="JB80" t="n">
         <v>0.4399999999999999</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.02035980671644211</v>
+        <v>0.003544200211763382</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0.8422177498126892</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.0006294287741184235</v>
+        <v>-7.085129618644714e-05</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
         <v>0.8422181095912892</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.008259594440460205</v>
+        <v>-0.009049899876117706</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0.8422181303477468</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.0142652653157711</v>
+        <v>-0.01494373753666878</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001939624547958374</v>
+        <v>-0.002351466566324234</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.004651501774787903</v>
+        <v>-0.004250060766935349</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.02596906200051308</v>
+        <v>0.02526293322443962</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.16</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0.8422183655876008</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.006125964224338531</v>
+        <v>-0.006722770631313324</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.004082027822732925</v>
+        <v>-0.004009116441011429</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0.8422186838532854</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.005552452057600021</v>
+        <v>-0.005365323275327682</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0.8422186008274546</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.02573654428124428</v>
+        <v>-0.003755025565624237</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
         <v>0.8422183932628778</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.02794375643134117</v>
+        <v>-0.001004010438919067</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8599999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0.8422184071005161</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.02676088735461235</v>
+        <v>-0.001809693872928619</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0.8422185454769009</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.02912146598100662</v>
+        <v>-0.001648887991905212</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0.8422182618053122</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.02835822850465775</v>
+        <v>0.02786834910511971</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0.8422180888348315</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.001730576157569885</v>
+        <v>0.001862980425357819</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0.842217985052543</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.02944717928767204</v>
+        <v>-0.0007461756467819214</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0.8422181303477468</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.02915409579873085</v>
+        <v>0.02862087264657021</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0.8422183725064202</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.02960276231169701</v>
+        <v>-0.0002099424600601196</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0.8422181995359391</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0296849999576807</v>
+        <v>0.02920147404074669</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0.8422179020267122</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.02937005832791328</v>
+        <v>0.004927795380353928</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0.8422178881890736</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.03123931586742401</v>
+        <v>0.03074469044804573</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.02000000000000007</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0.8422175214916544</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.02489614114165306</v>
+        <v>0.01850421354174614</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.02000000000000007</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
         <v>0.8422175214916544</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.008393201977014542</v>
+        <v>-0.009143635630607605</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.02000000000000007</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0308460034430027</v>
+        <v>0.03030569478869438</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
         <v>0.8422173554399929</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.03068006783723831</v>
+        <v>0.030220877379179</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.16</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
         <v>0.842217182469512</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.005868095904588699</v>
+        <v>0.007062934339046478</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0.8422172309012467</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.03441732004284859</v>
+        <v>0.03383643180131912</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.02000000000000007</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0.8422168711226466</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.03066841699182987</v>
+        <v>0.03021242469549179</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0.8422168296097312</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.02844017744064331</v>
+        <v>0.01495148241519928</v>
       </c>
       <c r="JB110" t="n">
         <v>0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.03194884955883026</v>
+        <v>0.03147219866514206</v>
       </c>
       <c r="JB111" t="n">
         <v>0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.04098686203360558</v>
+        <v>0.04048921912908554</v>
       </c>
       <c r="JB112" t="n">
         <v>0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.03673569113016129</v>
+        <v>0.03627220541238785</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.04104301333427429</v>
+        <v>0.0405774787068367</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.04046512395143509</v>
+        <v>0.03999077528715134</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.04020074382424355</v>
+        <v>0.03972186893224716</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.03057575412094593</v>
+        <v>0.03017874248325825</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02906996011734009</v>
+        <v>0.02957335859537125</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.4399999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.01411747559905052</v>
+        <v>-0.02854334935545921</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.008495412766933441</v>
+        <v>0.00775359570980072</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.8599999999999999</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.004064943641424179</v>
+        <v>0.003971852362155914</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0.8422171340377773</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.003830190747976303</v>
+        <v>0.004462122917175293</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.03032876923680305</v>
+        <v>0.02982746809720993</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.02901438251137733</v>
+        <v>0.008485611528158188</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.16</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0.8422168157720926</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.03119392320513725</v>
+        <v>0.03071192279458046</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7900000000000004</v>
+        <v>0.7200000000000002</v>
       </c>
       <c r="JC125" t="n">
         <v>0.8422168572850081</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.06000718474388123</v>
+        <v>0.03718722239136696</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
         <v>0.8422168849602849</v>
